--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118732274</v>
+        <v>118732345</v>
       </c>
       <c r="B2" t="n">
-        <v>104940</v>
+        <v>91127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27145, Sm</t>
+          <t>A 27145, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579895</v>
+        <v>579861</v>
       </c>
       <c r="R2" t="n">
-        <v>6398516</v>
+        <v>6398551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118732421</v>
+        <v>118732274</v>
       </c>
       <c r="B3" t="n">
         <v>104940</v>
@@ -830,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27145,  Ankarsrum, Sm</t>
+          <t>A 27145, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579688</v>
+        <v>579895</v>
       </c>
       <c r="R3" t="n">
-        <v>6398462</v>
+        <v>6398516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1012,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118732345</v>
+        <v>118732421</v>
       </c>
       <c r="B5" t="n">
-        <v>91127</v>
+        <v>104940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,45 +1031,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>A 27145,  Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579861</v>
+        <v>579688</v>
       </c>
       <c r="R5" t="n">
-        <v>6398551</v>
+        <v>6398462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,6 +1123,227 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118890909</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94620</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579675</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398816</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118890876</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579629</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398805</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118732345</v>
+        <v>118732274</v>
       </c>
       <c r="B2" t="n">
-        <v>91127</v>
+        <v>104940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>A 27145, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579861</v>
+        <v>579895</v>
       </c>
       <c r="R2" t="n">
-        <v>6398551</v>
+        <v>6398516</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118732274</v>
+        <v>118732421</v>
       </c>
       <c r="B3" t="n">
         <v>104940</v>
@@ -833,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27145, Sm</t>
+          <t>A 27145,  Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579895</v>
+        <v>579688</v>
       </c>
       <c r="R3" t="n">
-        <v>6398516</v>
+        <v>6398462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1015,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118732421</v>
+        <v>118732345</v>
       </c>
       <c r="B5" t="n">
-        <v>104940</v>
+        <v>91127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,42 +1028,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27145,  Ankarsrum, Sm</t>
+          <t>A 27145, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579688</v>
+        <v>579861</v>
       </c>
       <c r="R5" t="n">
-        <v>6398462</v>
+        <v>6398551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118890909</v>
+        <v>118890876</v>
       </c>
       <c r="B6" t="n">
-        <v>94620</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,31 +1138,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579675</v>
+        <v>579629</v>
       </c>
       <c r="R6" t="n">
-        <v>6398816</v>
+        <v>6398805</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118890876</v>
+        <v>118890909</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>94620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1252,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579629</v>
+        <v>579675</v>
       </c>
       <c r="R7" t="n">
-        <v>6398805</v>
+        <v>6398816</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118732274</v>
+        <v>118732421</v>
       </c>
       <c r="B2" t="n">
-        <v>104940</v>
+        <v>104947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27145, Sm</t>
+          <t>A 27145,  Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579895</v>
+        <v>579688</v>
       </c>
       <c r="R2" t="n">
-        <v>6398516</v>
+        <v>6398462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118732421</v>
+        <v>118732274</v>
       </c>
       <c r="B3" t="n">
-        <v>104940</v>
+        <v>104947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27145,  Ankarsrum, Sm</t>
+          <t>A 27145, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579688</v>
+        <v>579895</v>
       </c>
       <c r="R3" t="n">
-        <v>6398462</v>
+        <v>6398516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118732323</v>
+        <v>118732345</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>91134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579866</v>
+        <v>579861</v>
       </c>
       <c r="R4" t="n">
-        <v>6398525</v>
+        <v>6398551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,17 +986,13 @@
           <t>2024-07-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I död stående tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118732345</v>
+        <v>118732323</v>
       </c>
       <c r="B5" t="n">
-        <v>91127</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579861</v>
+        <v>579866</v>
       </c>
       <c r="R5" t="n">
-        <v>6398551</v>
+        <v>6398525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,13 +1097,17 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I död stående tall</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118890876</v>
+        <v>118890909</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>94627</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,39 +1138,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579629</v>
+        <v>579675</v>
       </c>
       <c r="R6" t="n">
-        <v>6398805</v>
+        <v>6398816</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118890909</v>
+        <v>118890876</v>
       </c>
       <c r="B7" t="n">
-        <v>94620</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,31 +1245,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579675</v>
+        <v>579629</v>
       </c>
       <c r="R7" t="n">
-        <v>6398816</v>
+        <v>6398805</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,1585 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118980113</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579703</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398460</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118980250</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398395</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118980173</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97853</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398438</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118980222</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90006</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579795</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398390</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118980099</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579692</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398471</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118980335</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579904</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398411</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat gran med hästmyror.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118980118</v>
+      </c>
+      <c r="B14" t="n">
+        <v>94627</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118980131</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579698</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398463</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118980289</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579902</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398411</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118980032</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94627</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579783</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398578</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118980000</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579915</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398440</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118980050</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579661</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6398492</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118980145</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579726</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6398452</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118980197</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579786</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6398428</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118732421</v>
+        <v>118732323</v>
       </c>
       <c r="B2" t="n">
-        <v>104947</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27145,  Ankarsrum, Sm</t>
+          <t>A 27145, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579688</v>
+        <v>579866</v>
       </c>
       <c r="R2" t="n">
-        <v>6398462</v>
+        <v>6398525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,13 +761,17 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I död stående tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118732323</v>
+        <v>118732421</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>104947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,46 +1027,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>A 27145,  Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579866</v>
+        <v>579688</v>
       </c>
       <c r="R5" t="n">
-        <v>6398525</v>
+        <v>6398462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,17 +1101,13 @@
           <t>2024-07-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I död stående tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118890909</v>
+        <v>118890876</v>
       </c>
       <c r="B6" t="n">
-        <v>94627</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,31 +1138,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579675</v>
+        <v>579629</v>
       </c>
       <c r="R6" t="n">
-        <v>6398816</v>
+        <v>6398805</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118890876</v>
+        <v>118890909</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>94627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1252,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579629</v>
+        <v>579675</v>
       </c>
       <c r="R7" t="n">
-        <v>6398805</v>
+        <v>6398816</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118980113</v>
+        <v>118980222</v>
       </c>
       <c r="B8" t="n">
-        <v>104947</v>
+        <v>90006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,39 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>2051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579703</v>
+        <v>579795</v>
       </c>
       <c r="R8" t="n">
-        <v>6398460</v>
+        <v>6398390</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118980250</v>
+        <v>118980118</v>
       </c>
       <c r="B9" t="n">
-        <v>90511</v>
+        <v>94627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,38 +1473,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579781</v>
+        <v>579714</v>
       </c>
       <c r="R9" t="n">
-        <v>6398395</v>
+        <v>6398458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,11 +1541,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118980173</v>
+        <v>118980050</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,39 +1580,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1633,13 +1620,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579773</v>
+        <v>579661</v>
       </c>
       <c r="R10" t="n">
-        <v>6398438</v>
+        <v>6398492</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,7 +1664,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1696,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118980222</v>
+        <v>118980099</v>
       </c>
       <c r="B11" t="n">
-        <v>90006</v>
+        <v>104947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,38 +1694,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1747,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579795</v>
+        <v>579692</v>
       </c>
       <c r="R11" t="n">
-        <v>6398390</v>
+        <v>6398471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118980099</v>
+        <v>118980000</v>
       </c>
       <c r="B12" t="n">
         <v>104947</v>
@@ -1849,11 +1836,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1862,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579692</v>
+        <v>579915</v>
       </c>
       <c r="R12" t="n">
-        <v>6398471</v>
+        <v>6398440</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118980335</v>
+        <v>118980173</v>
       </c>
       <c r="B13" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,35 +1920,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1973,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579904</v>
+        <v>579773</v>
       </c>
       <c r="R13" t="n">
-        <v>6398411</v>
+        <v>6398438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,17 +1998,13 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat gran med hästmyror.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118980118</v>
+        <v>118980145</v>
       </c>
       <c r="B14" t="n">
-        <v>94627</v>
+        <v>104947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2039,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2084,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579714</v>
+        <v>579726</v>
       </c>
       <c r="R14" t="n">
-        <v>6398458</v>
+        <v>6398452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118980131</v>
+        <v>118980335</v>
       </c>
       <c r="B15" t="n">
-        <v>104947</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,35 +2146,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2195,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579698</v>
+        <v>579904</v>
       </c>
       <c r="R15" t="n">
-        <v>6398463</v>
+        <v>6398411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,13 +2220,17 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bearbetat gran med hästmyror.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2372,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118980032</v>
+        <v>118980250</v>
       </c>
       <c r="B17" t="n">
-        <v>94627</v>
+        <v>90511</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,31 +2375,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2416,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579783</v>
+        <v>579781</v>
       </c>
       <c r="R17" t="n">
-        <v>6398578</v>
+        <v>6398395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,6 +2450,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2482,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118980000</v>
+        <v>118980197</v>
       </c>
       <c r="B18" t="n">
         <v>104947</v>
@@ -2527,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579915</v>
+        <v>579786</v>
       </c>
       <c r="R18" t="n">
-        <v>6398440</v>
+        <v>6398428</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118980050</v>
+        <v>118980032</v>
       </c>
       <c r="B19" t="n">
-        <v>57443</v>
+        <v>94627</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,39 +2605,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2642,13 +2637,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579661</v>
+        <v>579783</v>
       </c>
       <c r="R19" t="n">
-        <v>6398492</v>
+        <v>6398578</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,6 +2681,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2704,7 +2700,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118980145</v>
+        <v>118980131</v>
       </c>
       <c r="B20" t="n">
         <v>104947</v>
@@ -2752,10 +2748,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579726</v>
+        <v>579698</v>
       </c>
       <c r="R20" t="n">
-        <v>6398452</v>
+        <v>6398463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2811,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118980197</v>
+        <v>118980113</v>
       </c>
       <c r="B21" t="n">
         <v>104947</v>
@@ -2854,7 +2850,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579786</v>
+        <v>579703</v>
       </c>
       <c r="R21" t="n">
-        <v>6398428</v>
+        <v>6398460</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,6 +2923,1242 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119005029</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57298</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579631</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6398487</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119005152</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96810</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579774</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6398439</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119005039</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104949</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>579665</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6398492</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>119005111</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104949</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>579715</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6398460</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119005123</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91133</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579758</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6398478</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>119005201</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90513</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579792</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6398480</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>119005137</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90908</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>579757</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6398471</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119005141</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104949</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>579757</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6398471</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>119005218</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>579889</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6398517</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119005164</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104949</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>579779</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6398432</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119005192</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57308</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>579789</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6398451</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>118980222</v>
       </c>
       <c r="B19" t="n">
-        <v>90181</v>
+        <v>90191</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>118980222</v>
       </c>
       <c r="B19" t="n">
-        <v>90191</v>
+        <v>90203</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -3823,7 +3823,7 @@
         <v>119005029</v>
       </c>
       <c r="B30" t="n">
-        <v>57314</v>
+        <v>57484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -3823,7 +3823,7 @@
         <v>119005029</v>
       </c>
       <c r="B30" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -3823,7 +3823,7 @@
         <v>119005029</v>
       </c>
       <c r="B30" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -3823,7 +3823,7 @@
         <v>119005029</v>
       </c>
       <c r="B30" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2024 artfynd.xlsx
+++ b/artfynd/A 27145-2024 artfynd.xlsx
@@ -3823,7 +3823,7 @@
         <v>119005029</v>
       </c>
       <c r="B30" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
